--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -4126,12 +4126,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4156,35 +4156,35 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_703_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_703_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Virale infeksjoner i sentralnervesystemet</t>
+          <t>Viral meningoencefalit</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4244,17 +4244,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+          <t>SE_FOHM_SMINET_VME_excluding_TBE_from_2021</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+          <t>Swedish viral meningoencephalitis aggregate from 2021 onward, explicitly excluding TBE.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4277,49 +4277,276 @@
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
         <v>1</v>
       </c>
-      <c r="AU17" t="inlineStr">
+      <c r="AU18" t="inlineStr">
         <is>
           <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
-      <c r="AV17" t="inlineStr">
+      <c r="AV18" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW17" t="inlineStr">
+      <c r="AW18" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
+      <c r="AY18" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA17" t="inlineStr">
+      <c r="BA18" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB17" t="inlineStr">
+      <c r="BB18" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC17" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -4451,7 +4678,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -4471,7 +4698,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>

--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>

--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>

--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">

--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4547,6 +4547,460 @@
         </is>
       </c>
       <c r="BC18" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>79</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Viral meningoencefalit</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_VME_excluding_TBE_from_2021</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Swedish viral meningoencephalitis aggregate from 2021 onward, explicitly excluding TBE.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -4585,7 +5039,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -4678,7 +5132,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -4698,7 +5152,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>

--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -943,7 +943,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -989,34 +989,15 @@
       <c r="N3" t="n">
         <v>47</v>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O3" t="n">
+        <v>47</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.4392093801293172</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1024,86 +1005,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_excluding_TBE_from_2021</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate from 2021 onward, explicitly excluding TBE.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
-        <v>0</v>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1397,7 +1320,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1443,34 +1366,15 @@
       <c r="N5" t="n">
         <v>31</v>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O5" t="n">
+        <v>31</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2896912932767837</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1478,86 +1382,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_excluding_TBE_from_2021</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate from 2021 onward, explicitly excluding TBE.</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN5" t="b">
-        <v>0</v>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1851,7 +1697,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1897,34 +1743,15 @@
       <c r="N7" t="n">
         <v>41</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O7" t="n">
+        <v>41</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3831400975596171</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1932,86 +1759,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_excluding_TBE_from_2021</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate from 2021 onward, explicitly excluding TBE.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN7" t="b">
-        <v>0</v>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2305,7 +2074,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2351,34 +2120,15 @@
       <c r="N9" t="n">
         <v>41</v>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O9" t="n">
+        <v>41</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3831400975596171</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -2386,86 +2136,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_excluding_TBE_from_2021</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate from 2021 onward, explicitly excluding TBE.</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>0</v>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2759,7 +2451,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2805,34 +2497,15 @@
       <c r="N11" t="n">
         <v>47</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O11" t="n">
+        <v>47</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4392093801293172</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2840,86 +2513,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_excluding_TBE_from_2021</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate from 2021 onward, explicitly excluding TBE.</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN11" t="b">
-        <v>0</v>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3213,7 +2828,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3259,34 +2874,15 @@
       <c r="N13" t="n">
         <v>59</v>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O13" t="n">
+        <v>59</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.5513479452687174</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -3294,86 +2890,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_excluding_TBE_from_2021</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate from 2021 onward, explicitly excluding TBE.</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN13" t="b">
-        <v>0</v>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -3667,7 +3205,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3713,34 +3251,15 @@
       <c r="N15" t="n">
         <v>90</v>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O15" t="n">
+        <v>90</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.8410392385455011</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -3748,86 +3267,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_excluding_TBE_from_2021</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate from 2021 onward, explicitly excluding TBE.</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN15" t="b">
-        <v>0</v>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -4121,7 +3582,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4167,34 +3628,15 @@
       <c r="N17" t="n">
         <v>71</v>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O17" t="n">
+        <v>71</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6634865104081176</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -4202,86 +3644,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_excluding_TBE_from_2021</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate from 2021 onward, explicitly excluding TBE.</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN17" t="b">
-        <v>0</v>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -4575,7 +3959,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4621,34 +4005,15 @@
       <c r="N19" t="n">
         <v>79</v>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_FROM_2021</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O19" t="n">
+        <v>79</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.7382455538343843</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -4656,86 +4021,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_excluding_TBE_from_2021</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate from 2021 onward, explicitly excluding TBE.</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN19" t="b">
-        <v>0</v>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5122,7 +4429,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -5152,7 +4459,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -5162,7 +4469,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5173,7 +4480,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
     </row>
@@ -5184,7 +4491,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -760,71 +760,163 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
-      </c>
-      <c r="O2" t="n">
-        <v>47</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.4392093801293172</v>
+        <v>23</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN2" t="b">
+        <v>0</v>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -886,22 +978,27 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2896912932767837</v>
+        <v>0.4392093801293172</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -915,13 +1012,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>fohm_sminet</t>
@@ -986,17 +1093,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1021,80 +1128,172 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>41</v>
-      </c>
-      <c r="O4" t="n">
-        <v>41</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.3831400975596171</v>
+        <v>19</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN4" t="b">
+        <v>0</v>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -1156,22 +1355,27 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="O5" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3831400975596171</v>
+        <v>0.2896912932767837</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1185,13 +1389,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>fohm_sminet</t>
@@ -1256,17 +1470,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1291,80 +1505,172 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>47</v>
-      </c>
-      <c r="O6" t="n">
-        <v>47</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.4392093801293172</v>
+        <v>22</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN6" t="b">
+        <v>0</v>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -1426,22 +1732,27 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="O7" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5513479452687174</v>
+        <v>0.3831400975596171</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1455,13 +1766,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>fohm_sminet</t>
@@ -1526,17 +1847,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1561,80 +1882,172 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>90</v>
-      </c>
-      <c r="O8" t="n">
-        <v>90</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.8410392385455011</v>
+        <v>32</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN8" t="b">
+        <v>0</v>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -1696,22 +2109,27 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="O9" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6634865104081176</v>
+        <v>0.3831400975596171</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1725,13 +2143,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>fohm_sminet</t>
@@ -1796,17 +2224,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1831,80 +2259,2057 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>79</v>
-      </c>
-      <c r="O10" t="n">
-        <v>79</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.7382455538343843</v>
+        <v>37</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN10" t="b">
+        <v>0</v>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>47</v>
+      </c>
+      <c r="O11" t="n">
+        <v>47</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4392093801293172</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AV10" t="inlineStr">
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
         <is>
           <t>fohm_sminet</t>
         </is>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>official_html_csv</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>fohm_sminet</t>
         </is>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>48</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>59</v>
+      </c>
+      <c r="O13" t="n">
+        <v>59</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.5513479452687174</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>57</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>90</v>
+      </c>
+      <c r="O15" t="n">
+        <v>90</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.8410392385455011</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>68</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>71</v>
+      </c>
+      <c r="O17" t="n">
+        <v>71</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6634865104081176</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>64</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>79</v>
+      </c>
+      <c r="O19" t="n">
+        <v>79</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.7382455538343843</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>35</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -1941,7 +4346,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -2034,7 +4439,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -2054,7 +4459,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -2064,7 +4469,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
